--- a/InputData/trans/BNoGP/BAU Number of Gas Pumps.xlsx
+++ b/InputData/trans/BNoGP/BAU Number of Gas Pumps.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdeng\Desktop\Dropbox_Free_Zone\EPS\Model Repos\eps-us\InputData\trans\BNoGP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\trans\BNoGP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{8D1B5AEA-3A11-463F-9E0D-2C706DCF7B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96A5EC34-F8AF-47CC-A691-97AA03173D24}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3EF477-89E8-49E5-BACF-11232431D97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="885" windowWidth="22950" windowHeight="13650" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31695" yWindow="4260" windowWidth="19200" windowHeight="11205" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>BNoEVC BAU Number of Gas Pumps</t>
   </si>
@@ -85,16 +85,13 @@
   </si>
   <si>
     <t>Protemus</t>
-  </si>
-  <si>
-    <t>^need source, going based on vibes rn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,18 +442,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -464,42 +461,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -517,15 +514,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A3388B-37EB-4A2B-9BBE-B542C0E447C8}">
   <dimension ref="A1:AG3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -626,7 +623,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -729,7 +726,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -738,9 +735,6 @@
       </c>
       <c r="F3" t="s">
         <v>13</v>
-      </c>
-      <c r="M3" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -754,12 +748,12 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AG2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -860,7 +854,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1005,15 +999,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -1157,14 +1142,46 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{232CCF61-C7C0-4632-80B9-B14B1D30FF64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{232CCF61-C7C0-4632-80B9-B14B1D30FF64}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{601A4963-D071-46F3-B44F-9B3FE2FCA2D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05DF1675-97ED-4433-A240-6D3AB0CE2980}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05DF1675-97ED-4433-A240-6D3AB0CE2980}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{601A4963-D071-46F3-B44F-9B3FE2FCA2D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>